--- a/data/risk_register_data.xlsx
+++ b/data/risk_register_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\ALY_6130\Ass_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\ALY_6130\github\6130_Group1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2E7FC7B-9932-4800-A10F-35F096E1A2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A471CB-FFCC-42A9-86F3-98BC16F0B90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{85D16804-304B-4546-B126-22060495B028}"/>
   </bookViews>
@@ -1502,7 +1502,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="58" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="18">
         <v>26</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="69.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="18">
         <v>27</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="58" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="18">
         <v>28</v>
       </c>
@@ -1610,7 +1610,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="69.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:26" ht="23.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="20">
         <v>29</v>
       </c>
@@ -1646,7 +1646,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="46.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="20">
         <v>30</v>
       </c>
@@ -1682,7 +1682,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="58" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="20">
         <v>31</v>
       </c>
@@ -1718,7 +1718,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="69.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="20">
         <v>32</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
